--- a/bdd1.xlsx
+++ b/bdd1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\control-asistencia\bot-telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAB12F4-7CDE-42F0-8EE3-F588713E3202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717ED41D-0E5F-4F85-9924-B5315E940D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>chat_id</t>
   </si>
@@ -89,6 +89,21 @@
   </si>
   <si>
     <t xml:space="preserve">VILLANUEVA MACHUCA FERNANDO </t>
+  </si>
+  <si>
+    <t>Villanueva</t>
+  </si>
+  <si>
+    <t>David Villanueva</t>
+  </si>
+  <si>
+    <t>Angel Venancio</t>
+  </si>
+  <si>
+    <t>Panchis</t>
+  </si>
+  <si>
+    <t>Rafa Rosas</t>
   </si>
 </sst>
 </file>
@@ -504,6 +519,10 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F26" si="0">""""&amp;A3&amp;""": {""chat_id"": "&amp;B3&amp;", ""nombre"": """&amp;C3&amp;"""},"</f>
+        <v>"23318050270185": {"chat_id": 3241116031, "nombre": "CAMPILLO RODRIGUEZ ANGEL SLASH"},</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
@@ -515,6 +534,10 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270088": {"chat_id": 3241336452, "nombre": "DEL RIO ALATORRE AURELIANO"},</v>
+      </c>
       <c r="K4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -527,6 +550,10 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270229": {"chat_id": 3241117018, "nombre": "DELGADO JAIME SANTIAGO RAFAEL"},</v>
+      </c>
       <c r="K5"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -539,6 +566,10 @@
       <c r="C6" t="s">
         <v>6</v>
       </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270157": {"chat_id": 3241337966, "nombre": "ESTEBAN ROSALES CHRISTOPHER MARIO"},</v>
+      </c>
       <c r="K6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -551,6 +582,10 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270309": {"chat_id": 3241704201, "nombre": "GARCIA MARMOLEJO EDUARDO "},</v>
+      </c>
       <c r="K7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -563,6 +598,10 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270136": {"chat_id": 3241704178, "nombre": "GARCIA RAMIREZ ANGEL RAFAEL"},</v>
+      </c>
       <c r="K8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -575,6 +614,10 @@
       <c r="C9" t="s">
         <v>9</v>
       </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270187": {"chat_id": 3241056488, "nombre": "GONZALEZ PEÑA RUBEN "},</v>
+      </c>
       <c r="K9"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -587,6 +630,10 @@
       <c r="C10" t="s">
         <v>10</v>
       </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270155": {"chat_id": 3241169589, "nombre": "MEDA RAMOS CESAR ANTONIO"},</v>
+      </c>
       <c r="K10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -599,6 +646,10 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270175": {"chat_id": 3241160921, "nombre": "MORA HERNANDEZ LINO "},</v>
+      </c>
       <c r="K11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -611,6 +662,10 @@
       <c r="C12" t="s">
         <v>12</v>
       </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270218": {"chat_id": 3241005047, "nombre": "MORENO JAIME EDGAR EMILIANO"},</v>
+      </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -623,6 +678,10 @@
       <c r="C13" t="s">
         <v>13</v>
       </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270121": {"chat_id": 3241969133, "nombre": "NAJAR MARIN LUCERO GUADALUPE"},</v>
+      </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -635,6 +694,10 @@
       <c r="C14" t="s">
         <v>14</v>
       </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270242": {"chat_id": 3241336381, "nombre": "NUÑEZ GONZALEZ ALEXIS DANIEL"},</v>
+      </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -647,6 +710,10 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270147": {"chat_id": 3241140087, "nombre": "ORNELAS BECERRA JANETH VANESA"},</v>
+      </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -659,6 +726,10 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270096": {"chat_id": 3241336375, "nombre": "RIVERA PEREZ JESUS GADIEL"},</v>
+      </c>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -671,6 +742,10 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270095": {"chat_id": 3241709800, "nombre": "SALAZAR LINARES MONTSERRAT GUADALUPE"},</v>
+      </c>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -683,6 +758,10 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270072": {"chat_id": 3241964346, "nombre": "SANTILLAN SALAS CHRISTIAN OMAR"},</v>
+      </c>
       <c r="K18"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -695,6 +774,10 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270137": {"chat_id": 7447523853, "nombre": "SOTO RODRIGUEZ MARIO ALEJANDRO"},</v>
+      </c>
       <c r="K19"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -707,6 +790,10 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270213": {"chat_id": 3241336257, "nombre": "TEJEDA PEÑA VICTOR MIGUEL"},</v>
+      </c>
       <c r="K20"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -719,6 +806,10 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270165": {"chat_id": 5656968141, "nombre": "VARGAS VILLA STEICE JAKELINE"},</v>
+      </c>
       <c r="K21"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -731,18 +822,77 @@
       <c r="C22" t="s">
         <v>22</v>
       </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>"23318050270099": {"chat_id": 3741164662, "nombre": "VILLANUEVA MACHUCA FERNANDO "},</v>
+      </c>
       <c r="K22"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>23300001</v>
+      </c>
+      <c r="B23">
+        <v>5539114333</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>"23300001": {"chat_id": 5539114333, "nombre": "David Villanueva"},</v>
+      </c>
       <c r="K23"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>23300002</v>
+      </c>
+      <c r="B24">
+        <v>6137041231</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>"23300002": {"chat_id": 6137041231, "nombre": "Angel Venancio"},</v>
+      </c>
       <c r="K24"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23300003</v>
+      </c>
+      <c r="B25">
+        <v>7729743648</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>"23300003": {"chat_id": 7729743648, "nombre": "Panchis"},</v>
+      </c>
       <c r="K25"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>23300004</v>
+      </c>
+      <c r="B26">
+        <v>8777068776</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>"23300004": {"chat_id": 8777068776, "nombre": "Rafa Rosas"},</v>
+      </c>
       <c r="K26"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
